--- a/artfynd/A 14450-2023 artfynd.xlsx
+++ b/artfynd/A 14450-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 14450-2023 artfynd.xlsx
+++ b/artfynd/A 14450-2023 artfynd.xlsx
@@ -13878,10 +13878,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>118772977</v>
+        <v>118772965</v>
       </c>
       <c r="B122" t="n">
-        <v>106120</v>
+        <v>108714</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13894,16 +13894,16 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -13923,7 +13923,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -13932,10 +13932,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>693063</v>
+        <v>693249</v>
       </c>
       <c r="R122" t="n">
-        <v>6359046</v>
+        <v>6358880</v>
       </c>
       <c r="S122" t="n">
         <v>3</v>
@@ -13999,10 +13999,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>118772980</v>
+        <v>118772977</v>
       </c>
       <c r="B123" t="n">
-        <v>108714</v>
+        <v>106120</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -14015,16 +14015,16 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -14032,10 +14032,19 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -14044,13 +14053,13 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>693207</v>
+        <v>693063</v>
       </c>
       <c r="R123" t="n">
-        <v>6359037</v>
+        <v>6359046</v>
       </c>
       <c r="S123" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -14363,10 +14372,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>118772974</v>
+        <v>118772973</v>
       </c>
       <c r="B126" t="n">
-        <v>106776</v>
+        <v>108714</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14379,27 +14388,27 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -14475,10 +14484,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>118772973</v>
+        <v>118772974</v>
       </c>
       <c r="B127" t="n">
-        <v>108714</v>
+        <v>106776</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14491,27 +14500,27 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
@@ -14587,10 +14596,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>118772978</v>
+        <v>118772980</v>
       </c>
       <c r="B128" t="n">
-        <v>106776</v>
+        <v>108714</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14603,31 +14612,27 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
@@ -14636,13 +14641,13 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>693171</v>
+        <v>693207</v>
       </c>
       <c r="R128" t="n">
-        <v>6359066</v>
+        <v>6359037</v>
       </c>
       <c r="S128" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -14672,11 +14677,6 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2024-07-02</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>inom 15 m</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14708,10 +14708,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>118772965</v>
+        <v>118772978</v>
       </c>
       <c r="B129" t="n">
-        <v>108714</v>
+        <v>106776</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14724,36 +14724,31 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>i frukt</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
@@ -14762,13 +14757,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>693249</v>
+        <v>693171</v>
       </c>
       <c r="R129" t="n">
-        <v>6358880</v>
+        <v>6359066</v>
       </c>
       <c r="S129" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14798,6 +14793,11 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>inom 15 m</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14829,7 +14829,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>118772968</v>
+        <v>118772971</v>
       </c>
       <c r="B130" t="n">
         <v>106776</v>
@@ -14864,17 +14864,17 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L130" t="inlineStr"/>
@@ -14885,13 +14885,13 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>693239</v>
+        <v>693183</v>
       </c>
       <c r="R130" t="n">
-        <v>6358916</v>
+        <v>6358972</v>
       </c>
       <c r="S130" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14953,7 +14953,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>118772971</v>
+        <v>118772968</v>
       </c>
       <c r="B131" t="n">
         <v>106776</v>
@@ -14988,17 +14988,17 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L131" t="inlineStr"/>
@@ -15009,13 +15009,13 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>693183</v>
+        <v>693239</v>
       </c>
       <c r="R131" t="n">
-        <v>6358972</v>
+        <v>6358916</v>
       </c>
       <c r="S131" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>

--- a/artfynd/A 14450-2023 artfynd.xlsx
+++ b/artfynd/A 14450-2023 artfynd.xlsx
@@ -13878,7 +13878,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>118772965</v>
+        <v>118772980</v>
       </c>
       <c r="B122" t="n">
         <v>108714</v>
@@ -13911,16 +13911,7 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="K122" t="inlineStr">
         <is>
           <t>i frukt</t>
@@ -13932,13 +13923,13 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>693249</v>
+        <v>693207</v>
       </c>
       <c r="R122" t="n">
-        <v>6358880</v>
+        <v>6359037</v>
       </c>
       <c r="S122" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13999,10 +13990,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>118772977</v>
+        <v>118772974</v>
       </c>
       <c r="B123" t="n">
-        <v>106120</v>
+        <v>106776</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -14015,36 +14006,27 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -14053,13 +14035,13 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>693063</v>
+        <v>693098</v>
       </c>
       <c r="R123" t="n">
-        <v>6359046</v>
+        <v>6358999</v>
       </c>
       <c r="S123" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -14120,10 +14102,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>118773232</v>
+        <v>118772976</v>
       </c>
       <c r="B124" t="n">
-        <v>42955</v>
+        <v>106776</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14136,41 +14118,36 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>101242</v>
+        <v>220079</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>friflygande</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
@@ -14179,10 +14156,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>693243</v>
+        <v>693032</v>
       </c>
       <c r="R124" t="n">
-        <v>6358880</v>
+        <v>6359058</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -14217,11 +14194,6 @@
           <t>2024-07-02</t>
         </is>
       </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Slitet ex.</t>
-        </is>
-      </c>
       <c r="AD124" t="b">
         <v>0</v>
       </c>
@@ -14233,7 +14205,7 @@
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>kalkbarrskog</t>
+          <t>Kalkbarrskog</t>
         </is>
       </c>
       <c r="AT124" t="inlineStr"/>
@@ -14251,7 +14223,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>118772976</v>
+        <v>118772978</v>
       </c>
       <c r="B125" t="n">
         <v>106776</v>
@@ -14286,7 +14258,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -14294,24 +14266,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Fröjel Hallgårds 1:2 3, Gtl</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>693032</v>
+        <v>693171</v>
       </c>
       <c r="R125" t="n">
-        <v>6359058</v>
+        <v>6359066</v>
       </c>
       <c r="S125" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -14341,6 +14308,11 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>inom 15 m</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14372,10 +14344,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>118772973</v>
+        <v>118773232</v>
       </c>
       <c r="B126" t="n">
-        <v>108714</v>
+        <v>42955</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14388,27 +14360,41 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>220299</v>
+        <v>101242</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -14417,10 +14403,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>693098</v>
+        <v>693243</v>
       </c>
       <c r="R126" t="n">
-        <v>6358999</v>
+        <v>6358880</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -14455,6 +14441,11 @@
           <t>2024-07-02</t>
         </is>
       </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>Slitet ex.</t>
+        </is>
+      </c>
       <c r="AD126" t="b">
         <v>0</v>
       </c>
@@ -14466,7 +14457,7 @@
       </c>
       <c r="AI126" t="inlineStr">
         <is>
-          <t>Kalkbarrskog</t>
+          <t>kalkbarrskog</t>
         </is>
       </c>
       <c r="AT126" t="inlineStr"/>
@@ -14477,17 +14468,17 @@
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson</t>
+          <t>Jörgen Petersson, Gun Ingmansson</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>118772974</v>
+        <v>118772965</v>
       </c>
       <c r="B127" t="n">
-        <v>106776</v>
+        <v>108714</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14500,27 +14491,36 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
@@ -14529,13 +14529,13 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>693098</v>
+        <v>693249</v>
       </c>
       <c r="R127" t="n">
-        <v>6358999</v>
+        <v>6358880</v>
       </c>
       <c r="S127" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -14596,10 +14596,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>118772980</v>
+        <v>118772977</v>
       </c>
       <c r="B128" t="n">
-        <v>108714</v>
+        <v>106120</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14612,16 +14612,16 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -14629,10 +14629,19 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr"/>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
@@ -14641,13 +14650,13 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>693207</v>
+        <v>693063</v>
       </c>
       <c r="R128" t="n">
-        <v>6359037</v>
+        <v>6359046</v>
       </c>
       <c r="S128" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -14708,10 +14717,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>118772978</v>
+        <v>118772973</v>
       </c>
       <c r="B129" t="n">
-        <v>106776</v>
+        <v>108714</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14724,31 +14733,27 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
@@ -14757,13 +14762,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>693171</v>
+        <v>693098</v>
       </c>
       <c r="R129" t="n">
-        <v>6359066</v>
+        <v>6358999</v>
       </c>
       <c r="S129" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14793,11 +14798,6 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2024-07-02</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>inom 15 m</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14829,10 +14829,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>118772971</v>
+        <v>118772969</v>
       </c>
       <c r="B130" t="n">
-        <v>106776</v>
+        <v>108714</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14845,36 +14845,36 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L130" t="inlineStr"/>
@@ -14885,13 +14885,13 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>693183</v>
+        <v>693235</v>
       </c>
       <c r="R130" t="n">
-        <v>6358972</v>
+        <v>6358938</v>
       </c>
       <c r="S130" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -15077,10 +15077,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>118772969</v>
+        <v>118772971</v>
       </c>
       <c r="B132" t="n">
-        <v>108714</v>
+        <v>106776</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -15093,36 +15093,36 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L132" t="inlineStr"/>
@@ -15133,13 +15133,13 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>693235</v>
+        <v>693183</v>
       </c>
       <c r="R132" t="n">
-        <v>6358938</v>
+        <v>6358972</v>
       </c>
       <c r="S132" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>

--- a/artfynd/A 14450-2023 artfynd.xlsx
+++ b/artfynd/A 14450-2023 artfynd.xlsx
@@ -13878,10 +13878,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>118772980</v>
+        <v>118772974</v>
       </c>
       <c r="B122" t="n">
-        <v>108714</v>
+        <v>106783</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13894,27 +13894,27 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="K122" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -13923,10 +13923,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>693207</v>
+        <v>693098</v>
       </c>
       <c r="R122" t="n">
-        <v>6359037</v>
+        <v>6358999</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -13990,10 +13990,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>118772974</v>
+        <v>118772976</v>
       </c>
       <c r="B123" t="n">
-        <v>106776</v>
+        <v>106783</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -14023,7 +14023,16 @@
           <t>(L.) Scop.</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K123" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -14035,10 +14044,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>693098</v>
+        <v>693032</v>
       </c>
       <c r="R123" t="n">
-        <v>6358999</v>
+        <v>6359058</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -14102,10 +14111,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>118772976</v>
+        <v>118773232</v>
       </c>
       <c r="B124" t="n">
-        <v>106776</v>
+        <v>42955</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14118,36 +14127,41 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>220079</v>
+        <v>101242</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
@@ -14156,10 +14170,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>693032</v>
+        <v>693243</v>
       </c>
       <c r="R124" t="n">
-        <v>6359058</v>
+        <v>6358880</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -14194,6 +14208,11 @@
           <t>2024-07-02</t>
         </is>
       </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Slitet ex.</t>
+        </is>
+      </c>
       <c r="AD124" t="b">
         <v>0</v>
       </c>
@@ -14205,7 +14224,7 @@
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>Kalkbarrskog</t>
+          <t>kalkbarrskog</t>
         </is>
       </c>
       <c r="AT124" t="inlineStr"/>
@@ -14226,7 +14245,7 @@
         <v>118772978</v>
       </c>
       <c r="B125" t="n">
-        <v>106776</v>
+        <v>106783</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14344,10 +14363,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>118773232</v>
+        <v>118772980</v>
       </c>
       <c r="B126" t="n">
-        <v>42955</v>
+        <v>108721</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14360,41 +14379,27 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>101242</v>
+        <v>220299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>friflygande</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -14403,10 +14408,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>693243</v>
+        <v>693207</v>
       </c>
       <c r="R126" t="n">
-        <v>6358880</v>
+        <v>6359037</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -14441,11 +14446,6 @@
           <t>2024-07-02</t>
         </is>
       </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>Slitet ex.</t>
-        </is>
-      </c>
       <c r="AD126" t="b">
         <v>0</v>
       </c>
@@ -14457,7 +14457,7 @@
       </c>
       <c r="AI126" t="inlineStr">
         <is>
-          <t>kalkbarrskog</t>
+          <t>Kalkbarrskog</t>
         </is>
       </c>
       <c r="AT126" t="inlineStr"/>
@@ -14468,17 +14468,17 @@
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Jörgen Petersson, Gun Ingmansson</t>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>118772965</v>
+        <v>118772973</v>
       </c>
       <c r="B127" t="n">
-        <v>108714</v>
+        <v>108721</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14508,16 +14508,7 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
         <is>
           <t>i frukt</t>
@@ -14529,13 +14520,13 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>693249</v>
+        <v>693098</v>
       </c>
       <c r="R127" t="n">
-        <v>6358880</v>
+        <v>6358999</v>
       </c>
       <c r="S127" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -14596,10 +14587,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>118772977</v>
+        <v>118772965</v>
       </c>
       <c r="B128" t="n">
-        <v>106120</v>
+        <v>108721</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14612,16 +14603,16 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -14641,7 +14632,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
@@ -14650,10 +14641,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>693063</v>
+        <v>693249</v>
       </c>
       <c r="R128" t="n">
-        <v>6359046</v>
+        <v>6358880</v>
       </c>
       <c r="S128" t="n">
         <v>3</v>
@@ -14717,10 +14708,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>118772973</v>
+        <v>118772977</v>
       </c>
       <c r="B129" t="n">
-        <v>108714</v>
+        <v>106127</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14733,16 +14724,16 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -14750,10 +14741,19 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr"/>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
@@ -14762,13 +14762,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>693098</v>
+        <v>693063</v>
       </c>
       <c r="R129" t="n">
-        <v>6358999</v>
+        <v>6359046</v>
       </c>
       <c r="S129" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
         <v>118772969</v>
       </c>
       <c r="B130" t="n">
-        <v>108714</v>
+        <v>108721</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14953,10 +14953,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>118772968</v>
+        <v>118772971</v>
       </c>
       <c r="B131" t="n">
-        <v>106776</v>
+        <v>106783</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14988,17 +14988,17 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L131" t="inlineStr"/>
@@ -15009,13 +15009,13 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>693239</v>
+        <v>693183</v>
       </c>
       <c r="R131" t="n">
-        <v>6358916</v>
+        <v>6358972</v>
       </c>
       <c r="S131" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15077,10 +15077,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>118772971</v>
+        <v>118772968</v>
       </c>
       <c r="B132" t="n">
-        <v>106776</v>
+        <v>106783</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -15112,17 +15112,17 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L132" t="inlineStr"/>
@@ -15133,13 +15133,13 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>693183</v>
+        <v>693239</v>
       </c>
       <c r="R132" t="n">
-        <v>6358972</v>
+        <v>6358916</v>
       </c>
       <c r="S132" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>

--- a/artfynd/A 14450-2023 artfynd.xlsx
+++ b/artfynd/A 14450-2023 artfynd.xlsx
@@ -13990,10 +13990,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>118772976</v>
+        <v>118772977</v>
       </c>
       <c r="B123" t="n">
-        <v>106783</v>
+        <v>106127</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -14006,36 +14006,36 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -14044,13 +14044,13 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>693032</v>
+        <v>693063</v>
       </c>
       <c r="R123" t="n">
-        <v>6359058</v>
+        <v>6359046</v>
       </c>
       <c r="S123" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -14111,10 +14111,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>118773232</v>
+        <v>118772973</v>
       </c>
       <c r="B124" t="n">
-        <v>42955</v>
+        <v>108721</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14127,41 +14127,27 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>101242</v>
+        <v>220299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="K124" t="inlineStr">
         <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>friflygande</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
@@ -14170,10 +14156,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>693243</v>
+        <v>693098</v>
       </c>
       <c r="R124" t="n">
-        <v>6358880</v>
+        <v>6358999</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -14208,11 +14194,6 @@
           <t>2024-07-02</t>
         </is>
       </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Slitet ex.</t>
-        </is>
-      </c>
       <c r="AD124" t="b">
         <v>0</v>
       </c>
@@ -14224,7 +14205,7 @@
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>kalkbarrskog</t>
+          <t>Kalkbarrskog</t>
         </is>
       </c>
       <c r="AT124" t="inlineStr"/>
@@ -14242,10 +14223,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>118772978</v>
+        <v>118772980</v>
       </c>
       <c r="B125" t="n">
-        <v>106783</v>
+        <v>108721</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14258,31 +14239,27 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
@@ -14291,13 +14268,13 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>693171</v>
+        <v>693207</v>
       </c>
       <c r="R125" t="n">
-        <v>6359066</v>
+        <v>6359037</v>
       </c>
       <c r="S125" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -14327,11 +14304,6 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2024-07-02</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>inom 15 m</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14363,7 +14335,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>118772980</v>
+        <v>118772965</v>
       </c>
       <c r="B126" t="n">
         <v>108721</v>
@@ -14396,7 +14368,16 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr"/>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K126" t="inlineStr">
         <is>
           <t>i frukt</t>
@@ -14408,13 +14389,13 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>693207</v>
+        <v>693249</v>
       </c>
       <c r="R126" t="n">
-        <v>6359037</v>
+        <v>6358880</v>
       </c>
       <c r="S126" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -14475,10 +14456,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>118772973</v>
+        <v>118772976</v>
       </c>
       <c r="B127" t="n">
-        <v>108721</v>
+        <v>106783</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14491,27 +14472,36 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
@@ -14520,10 +14510,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>693098</v>
+        <v>693032</v>
       </c>
       <c r="R127" t="n">
-        <v>6358999</v>
+        <v>6359058</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -14587,10 +14577,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>118772965</v>
+        <v>118773232</v>
       </c>
       <c r="B128" t="n">
-        <v>108721</v>
+        <v>42955</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14603,21 +14593,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>220299</v>
+        <v>101242</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -14627,12 +14617,17 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
@@ -14641,13 +14636,13 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>693249</v>
+        <v>693243</v>
       </c>
       <c r="R128" t="n">
         <v>6358880</v>
       </c>
       <c r="S128" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -14679,6 +14674,11 @@
           <t>2024-07-02</t>
         </is>
       </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>Slitet ex.</t>
+        </is>
+      </c>
       <c r="AD128" t="b">
         <v>0</v>
       </c>
@@ -14690,7 +14690,7 @@
       </c>
       <c r="AI128" t="inlineStr">
         <is>
-          <t>Kalkbarrskog</t>
+          <t>kalkbarrskog</t>
         </is>
       </c>
       <c r="AT128" t="inlineStr"/>
@@ -14708,10 +14708,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>118772977</v>
+        <v>118772978</v>
       </c>
       <c r="B129" t="n">
-        <v>106127</v>
+        <v>106783</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14724,36 +14724,31 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
@@ -14762,13 +14757,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>693063</v>
+        <v>693171</v>
       </c>
       <c r="R129" t="n">
-        <v>6359046</v>
+        <v>6359066</v>
       </c>
       <c r="S129" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14798,6 +14793,11 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>inom 15 m</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14829,10 +14829,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>118772969</v>
+        <v>118772971</v>
       </c>
       <c r="B130" t="n">
-        <v>108721</v>
+        <v>106783</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14845,36 +14845,36 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L130" t="inlineStr"/>
@@ -14885,13 +14885,13 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>693235</v>
+        <v>693183</v>
       </c>
       <c r="R130" t="n">
-        <v>6358938</v>
+        <v>6358972</v>
       </c>
       <c r="S130" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14953,10 +14953,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>118772971</v>
+        <v>118772969</v>
       </c>
       <c r="B131" t="n">
-        <v>106783</v>
+        <v>108721</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14969,36 +14969,36 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L131" t="inlineStr"/>
@@ -15009,13 +15009,13 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>693183</v>
+        <v>693235</v>
       </c>
       <c r="R131" t="n">
-        <v>6358972</v>
+        <v>6358938</v>
       </c>
       <c r="S131" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>

--- a/artfynd/A 14450-2023 artfynd.xlsx
+++ b/artfynd/A 14450-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY132"/>
+  <dimension ref="A1:AY155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15199,6 +15199,2499 @@
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>120631630</v>
+      </c>
+      <c r="B133" t="n">
+        <v>86373</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>Styrmansberget, Fröjel, Gtl</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>692965</v>
+      </c>
+      <c r="R133" t="n">
+        <v>6359323</v>
+      </c>
+      <c r="S133" t="n">
+        <v>10</v>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AD133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT133" t="inlineStr"/>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>Carl Jansson, Helena Björnström, Uno Skog, Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>120631622</v>
+      </c>
+      <c r="B134" t="n">
+        <v>86449</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Styrmansberget, Fröjel, Gtl</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>693000</v>
+      </c>
+      <c r="R134" t="n">
+        <v>6359215</v>
+      </c>
+      <c r="S134" t="n">
+        <v>10</v>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AD134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT134" t="inlineStr"/>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>Carl Jansson, Helena Björnström, Uno Skog, Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>120633938</v>
+      </c>
+      <c r="B135" t="n">
+        <v>86282</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>Styrmansberget Flöjel, Gtl</t>
+        </is>
+      </c>
+      <c r="Q135" t="n">
+        <v>693051</v>
+      </c>
+      <c r="R135" t="n">
+        <v>6359217</v>
+      </c>
+      <c r="S135" t="n">
+        <v>10</v>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AD135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT135" t="inlineStr"/>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>Uno Skog, Helena Björnström, Carl Jansson, Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>120631626</v>
+      </c>
+      <c r="B136" t="n">
+        <v>86373</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>Styrmansberget, Fröjel, Gtl</t>
+        </is>
+      </c>
+      <c r="Q136" t="n">
+        <v>692968</v>
+      </c>
+      <c r="R136" t="n">
+        <v>6359295</v>
+      </c>
+      <c r="S136" t="n">
+        <v>10</v>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AD136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT136" t="inlineStr"/>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>Carl Jansson, Helena Björnström, Uno Skog, Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>120631620</v>
+      </c>
+      <c r="B137" t="n">
+        <v>86373</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Styrmansberget, Fröjel, Gtl</t>
+        </is>
+      </c>
+      <c r="Q137" t="n">
+        <v>693002</v>
+      </c>
+      <c r="R137" t="n">
+        <v>6359215</v>
+      </c>
+      <c r="S137" t="n">
+        <v>10</v>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AD137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT137" t="inlineStr"/>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>Carl Jansson, Helena Björnström, Uno Skog, Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>120633917</v>
+      </c>
+      <c r="B138" t="n">
+        <v>86302</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>424</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Svartgrön spindling</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Styrmansberget Flöjel, Gtl</t>
+        </is>
+      </c>
+      <c r="Q138" t="n">
+        <v>693029</v>
+      </c>
+      <c r="R138" t="n">
+        <v>6359194</v>
+      </c>
+      <c r="S138" t="n">
+        <v>10</v>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AD138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT138" t="inlineStr"/>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>Uno Skog, Helena Björnström, Carl Jansson, Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>120619632</v>
+      </c>
+      <c r="B139" t="n">
+        <v>86302</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>424</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Svartgrön spindling</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>Styrmansberget Fröjel, Gtl</t>
+        </is>
+      </c>
+      <c r="Q139" t="n">
+        <v>692963</v>
+      </c>
+      <c r="R139" t="n">
+        <v>6359310</v>
+      </c>
+      <c r="S139" t="n">
+        <v>10</v>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT139" t="inlineStr"/>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>Uno Skog, Carl Jansson, Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>120633915</v>
+      </c>
+      <c r="B140" t="n">
+        <v>86465</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>248947</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Trollspindling</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Cortinarius subgracilis</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Moënne-Locc.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>Styrmansberget Flöjel, Gtl</t>
+        </is>
+      </c>
+      <c r="Q140" t="n">
+        <v>692971</v>
+      </c>
+      <c r="R140" t="n">
+        <v>6359323</v>
+      </c>
+      <c r="S140" t="n">
+        <v>10</v>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AD140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT140" t="inlineStr"/>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>Uno Skog, Helena Björnström, Carl Jansson, Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>120631628</v>
+      </c>
+      <c r="B141" t="n">
+        <v>86302</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>424</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Svartgrön spindling</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>Styrmansberget, Fröjel, Gtl</t>
+        </is>
+      </c>
+      <c r="Q141" t="n">
+        <v>692962</v>
+      </c>
+      <c r="R141" t="n">
+        <v>6359301</v>
+      </c>
+      <c r="S141" t="n">
+        <v>10</v>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AD141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT141" t="inlineStr"/>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>Carl Jansson, Helena Björnström, Uno Skog, Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>120633929</v>
+      </c>
+      <c r="B142" t="n">
+        <v>86373</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Styrmansberget Flöjel, Gtl</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>692988</v>
+      </c>
+      <c r="R142" t="n">
+        <v>6359257</v>
+      </c>
+      <c r="S142" t="n">
+        <v>10</v>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AD142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF142" t="inlineStr"/>
+      <c r="AG142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT142" t="inlineStr"/>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>Uno Skog, Helena Björnström, Carl Jansson, Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>120631632</v>
+      </c>
+      <c r="B143" t="n">
+        <v>90356</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>2015</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Vit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Hydnum albidum</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Peck</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Styrmansberget, Fröjel, Gtl</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>692876</v>
+      </c>
+      <c r="R143" t="n">
+        <v>6359275</v>
+      </c>
+      <c r="S143" t="n">
+        <v>10</v>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AD143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT143" t="inlineStr"/>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>Carl Jansson, Helena Björnström, Uno Skog, Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>120633922</v>
+      </c>
+      <c r="B144" t="n">
+        <v>88170</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>4962</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Mjölsvärting</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Lyophyllum semitale</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>(Fr. : Fr.) Kühner</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Styrmansberget Flöjel, Gtl</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>693025</v>
+      </c>
+      <c r="R144" t="n">
+        <v>6359240</v>
+      </c>
+      <c r="S144" t="n">
+        <v>10</v>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AD144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT144" t="inlineStr"/>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>Uno Skog, Helena Björnström, Carl Jansson, Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>120631631</v>
+      </c>
+      <c r="B145" t="n">
+        <v>86414</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>Styrmansberget, Fröjel, Gtl</t>
+        </is>
+      </c>
+      <c r="Q145" t="n">
+        <v>692957</v>
+      </c>
+      <c r="R145" t="n">
+        <v>6359332</v>
+      </c>
+      <c r="S145" t="n">
+        <v>10</v>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AD145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT145" t="inlineStr"/>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>Carl Jansson, Helena Björnström, Uno Skog, Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>120634096</v>
+      </c>
+      <c r="B146" t="n">
+        <v>86302</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>424</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Svartgrön spindling</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>Styrmansberget/Fröjel, Gtl</t>
+        </is>
+      </c>
+      <c r="Q146" t="n">
+        <v>692860</v>
+      </c>
+      <c r="R146" t="n">
+        <v>6359267</v>
+      </c>
+      <c r="S146" t="n">
+        <v>10</v>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AD146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT146" t="inlineStr"/>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>Andreas Öster, Helena Björnström, Carl Jansson, Uno Skog</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>120631625</v>
+      </c>
+      <c r="B147" t="n">
+        <v>86302</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>424</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Svartgrön spindling</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>Styrmansberget, Fröjel, Gtl</t>
+        </is>
+      </c>
+      <c r="Q147" t="n">
+        <v>692968</v>
+      </c>
+      <c r="R147" t="n">
+        <v>6359295</v>
+      </c>
+      <c r="S147" t="n">
+        <v>10</v>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AD147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT147" t="inlineStr"/>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>Carl Jansson, Helena Björnström, Uno Skog, Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>120631629</v>
+      </c>
+      <c r="B148" t="n">
+        <v>86325</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>433</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Duvspindling</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Cortinarius caesiocanescens</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>M. M. Moser</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Styrmansberget, Fröjel, Gtl</t>
+        </is>
+      </c>
+      <c r="Q148" t="n">
+        <v>692949</v>
+      </c>
+      <c r="R148" t="n">
+        <v>6359308</v>
+      </c>
+      <c r="S148" t="n">
+        <v>10</v>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AD148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT148" t="inlineStr"/>
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX148" t="inlineStr">
+        <is>
+          <t>Carl Jansson, Helena Björnström, Uno Skog, Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>120633916</v>
+      </c>
+      <c r="B149" t="n">
+        <v>86465</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>248947</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Trollspindling</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Cortinarius subgracilis</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Moënne-Locc.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>Styrmansberget Flöjel, Gtl</t>
+        </is>
+      </c>
+      <c r="Q149" t="n">
+        <v>692965</v>
+      </c>
+      <c r="R149" t="n">
+        <v>6359326</v>
+      </c>
+      <c r="S149" t="n">
+        <v>10</v>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AD149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT149" t="inlineStr"/>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX149" t="inlineStr">
+        <is>
+          <t>Uno Skog, Helena Björnström, Carl Jansson, Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>120633940</v>
+      </c>
+      <c r="B150" t="n">
+        <v>86282</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>Styrmansberget Flöjel, Gtl</t>
+        </is>
+      </c>
+      <c r="Q150" t="n">
+        <v>692883</v>
+      </c>
+      <c r="R150" t="n">
+        <v>6359283</v>
+      </c>
+      <c r="S150" t="n">
+        <v>10</v>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AD150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT150" t="inlineStr"/>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>Uno Skog, Helena Björnström, Carl Jansson, Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>120631623</v>
+      </c>
+      <c r="B151" t="n">
+        <v>89210</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>970</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Bittermusseron</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Leucopaxillus gentianeus</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>(Quél.) Kotl.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>Styrmansberget, Fröjel, Gtl</t>
+        </is>
+      </c>
+      <c r="Q151" t="n">
+        <v>692984</v>
+      </c>
+      <c r="R151" t="n">
+        <v>6359290</v>
+      </c>
+      <c r="S151" t="n">
+        <v>10</v>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AD151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT151" t="inlineStr"/>
+      <c r="AW151" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX151" t="inlineStr">
+        <is>
+          <t>Carl Jansson, Helena Björnström, Uno Skog, Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>120633924</v>
+      </c>
+      <c r="B152" t="n">
+        <v>74593</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr"/>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>Styrmansberget Flöjel, Gtl</t>
+        </is>
+      </c>
+      <c r="Q152" t="n">
+        <v>692971</v>
+      </c>
+      <c r="R152" t="n">
+        <v>6359314</v>
+      </c>
+      <c r="S152" t="n">
+        <v>10</v>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AD152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT152" t="inlineStr"/>
+      <c r="AW152" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX152" t="inlineStr">
+        <is>
+          <t>Uno Skog, Helena Björnström, Carl Jansson, Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>120633934</v>
+      </c>
+      <c r="B153" t="n">
+        <v>86325</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>433</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Duvspindling</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Cortinarius caesiocanescens</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>M. M. Moser</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>Styrmansberget Flöjel, Gtl</t>
+        </is>
+      </c>
+      <c r="Q153" t="n">
+        <v>693029</v>
+      </c>
+      <c r="R153" t="n">
+        <v>6359194</v>
+      </c>
+      <c r="S153" t="n">
+        <v>10</v>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AD153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT153" t="inlineStr"/>
+      <c r="AW153" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX153" t="inlineStr">
+        <is>
+          <t>Uno Skog, Helena Björnström, Carl Jansson, Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>120634087</v>
+      </c>
+      <c r="B154" t="n">
+        <v>90356</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>2015</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Vit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Hydnum albidum</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Peck</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>Styrmansberget/Fröjel, Gtl</t>
+        </is>
+      </c>
+      <c r="Q154" t="n">
+        <v>692898</v>
+      </c>
+      <c r="R154" t="n">
+        <v>6359294</v>
+      </c>
+      <c r="S154" t="n">
+        <v>10</v>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AD154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT154" t="inlineStr"/>
+      <c r="AW154" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX154" t="inlineStr">
+        <is>
+          <t>Andreas Öster, Helena Björnström, Carl Jansson, Uno Skog, Helena Björnström, Carl Jansson, Uno Skog</t>
+        </is>
+      </c>
+      <c r="AY154" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>120633930</v>
+      </c>
+      <c r="B155" t="n">
+        <v>86373</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>Styrmansberget Flöjel, Gtl</t>
+        </is>
+      </c>
+      <c r="Q155" t="n">
+        <v>693006</v>
+      </c>
+      <c r="R155" t="n">
+        <v>6359238</v>
+      </c>
+      <c r="S155" t="n">
+        <v>10</v>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AD155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF155" t="inlineStr"/>
+      <c r="AG155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT155" t="inlineStr"/>
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX155" t="inlineStr">
+        <is>
+          <t>Uno Skog, Helena Björnström, Carl Jansson, Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14450-2023 artfynd.xlsx
+++ b/artfynd/A 14450-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY181"/>
+  <dimension ref="A1:AY186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11258,48 +11258,69 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>112791663</v>
+        <v>134685906</v>
       </c>
       <c r="B104" t="n">
-        <v>5199</v>
+        <v>43472</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>105930</v>
+        <v>101242</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Fröjel-Sigdarve, Gtl</t>
+          <t>Fröjel, Hallgårds 1:2 (3), Gtl</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>692990</v>
+        <v>693052</v>
       </c>
       <c r="R104" t="n">
-        <v>6359229</v>
+        <v>6358964</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11323,12 +11344,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2023-10-14</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2023-10-14</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11337,70 +11358,88 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
-        </is>
-      </c>
-      <c r="AY104" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna Gotland</t>
-        </is>
-      </c>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>96929839</v>
+        <v>134685911</v>
       </c>
       <c r="B105" t="n">
-        <v>8455</v>
+        <v>43472</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>106545</v>
+        <v>101242</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Fröjel Ö, Gtl</t>
+          <t>Fröjel, Hallgårds 1:2 (3), Gtl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>693187</v>
+        <v>692976</v>
       </c>
       <c r="R105" t="n">
-        <v>6359025</v>
+        <v>6359131</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11424,12 +11463,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11438,63 +11477,85 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>116145613</v>
+        <v>134685915</v>
       </c>
       <c r="B106" t="n">
-        <v>111176</v>
+        <v>43472</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>219677</v>
+        <v>101242</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Fröjel Hallgårds 1:2 3, Gtl</t>
+          <t>Fröjel, Hallgårds 1:2 (3), Gtl</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>692935</v>
+        <v>693181</v>
       </c>
       <c r="R106" t="n">
-        <v>6359208</v>
+        <v>6358917</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -11521,12 +11582,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11535,71 +11596,88 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
-      </c>
-      <c r="AI106" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>116145614</v>
+        <v>134685916</v>
       </c>
       <c r="B107" t="n">
-        <v>111176</v>
+        <v>43472</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>219677</v>
+        <v>101242</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Fröjel Hallgårds 1:2 3, Gtl</t>
+          <t>Fröjel, Hallgårds 1:2 (3), Gtl</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>692887</v>
+        <v>693207</v>
       </c>
       <c r="R107" t="n">
-        <v>6359207</v>
+        <v>6358894</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11623,12 +11701,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11637,71 +11715,79 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
-      </c>
-      <c r="AI107" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>116145615</v>
+        <v>134685914</v>
       </c>
       <c r="B108" t="n">
-        <v>111176</v>
+        <v>58698</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>219677</v>
+        <v>103055</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Fröjel Hallgårds 1:2 3, Gtl</t>
+          <t>Fröjel, Hallgårds 1:2 (3), Gtl</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>692971</v>
+        <v>693124</v>
       </c>
       <c r="R108" t="n">
-        <v>6359323</v>
+        <v>6359167</v>
       </c>
       <c r="S108" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11725,17 +11811,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>I träd, finns flera mot norr</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11746,31 +11827,26 @@
       </c>
       <c r="AG108" t="b">
         <v>0</v>
-      </c>
-      <c r="AI108" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>116145620</v>
+        <v>112791663</v>
       </c>
       <c r="B109" t="n">
-        <v>111176</v>
+        <v>5199</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11778,37 +11854,37 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>219677</v>
+        <v>105930</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Fröjel Hallgårds 1:2 3, Gtl</t>
+          <t>Fröjel-Sigdarve, Gtl</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>693035</v>
+        <v>692990</v>
       </c>
       <c r="R109" t="n">
-        <v>6359233</v>
+        <v>6359229</v>
       </c>
       <c r="S109" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -11832,12 +11908,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2023-10-14</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2023-10-14</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11848,31 +11924,30 @@
       </c>
       <c r="AG109" t="b">
         <v>0</v>
-      </c>
-      <c r="AI109" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AY109" t="inlineStr"/>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>116145630</v>
+        <v>96929839</v>
       </c>
       <c r="B110" t="n">
-        <v>111176</v>
+        <v>8455</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11880,37 +11955,37 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>219677</v>
+        <v>106545</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Fröjel Hallgårds 1:2 3, Gtl</t>
+          <t>Fröjel Ö, Gtl</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>693048</v>
+        <v>693187</v>
       </c>
       <c r="R110" t="n">
-        <v>6359128</v>
+        <v>6359025</v>
       </c>
       <c r="S110" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -11934,12 +12009,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11950,28 +12025,23 @@
       </c>
       <c r="AG110" t="b">
         <v>0</v>
-      </c>
-      <c r="AI110" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>116145641</v>
+        <v>116145613</v>
       </c>
       <c r="B111" t="n">
         <v>111176</v>
@@ -12006,13 +12076,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>693103</v>
+        <v>692935</v>
       </c>
       <c r="R111" t="n">
-        <v>6359146</v>
+        <v>6359208</v>
       </c>
       <c r="S111" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12073,7 +12143,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>117684242</v>
+        <v>116145614</v>
       </c>
       <c r="B112" t="n">
         <v>111176</v>
@@ -12104,17 +12174,17 @@
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Fröjel, Hallgårds 1:2 (3) N-del, Gtl</t>
+          <t>Fröjel Hallgårds 1:2 3, Gtl</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>692948</v>
+        <v>692887</v>
       </c>
       <c r="R112" t="n">
-        <v>6359349</v>
+        <v>6359207</v>
       </c>
       <c r="S112" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12154,6 +12224,11 @@
       </c>
       <c r="AG112" t="b">
         <v>0</v>
+      </c>
+      <c r="AI112" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
@@ -12170,10 +12245,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>112720971</v>
+        <v>116145615</v>
       </c>
       <c r="B113" t="n">
-        <v>99141</v>
+        <v>111176</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12181,38 +12256,37 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>219862</v>
+        <v>219677</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Styrmansberget, Gtl</t>
+          <t>Fröjel Hallgårds 1:2 3, Gtl</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>693029</v>
+        <v>692971</v>
       </c>
       <c r="R113" t="n">
-        <v>6359252</v>
+        <v>6359323</v>
       </c>
       <c r="S113" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12236,12 +12310,17 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2023-10-14</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2023-10-14</t>
+          <t>2024-04-21</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>I träd, finns flera mot norr</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12252,26 +12331,31 @@
       </c>
       <c r="AG113" t="b">
         <v>0</v>
+      </c>
+      <c r="AI113" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>116145602</v>
+        <v>116145620</v>
       </c>
       <c r="B114" t="n">
-        <v>99147</v>
+        <v>111176</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12279,16 +12363,16 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>219864</v>
+        <v>219677</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -12296,31 +12380,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Fröjel Hallgårds 1:2 3, Gtl</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>693052</v>
+        <v>693035</v>
       </c>
       <c r="R114" t="n">
-        <v>6359090</v>
+        <v>6359233</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -12384,10 +12454,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>116145604</v>
+        <v>116145630</v>
       </c>
       <c r="B115" t="n">
-        <v>99147</v>
+        <v>111176</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12395,16 +12465,16 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>219864</v>
+        <v>219677</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -12412,34 +12482,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Fröjel Hallgårds 1:2 3, Gtl</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>693030</v>
+        <v>693048</v>
       </c>
       <c r="R115" t="n">
-        <v>6359101</v>
+        <v>6359128</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12500,10 +12556,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>116145605</v>
+        <v>116145641</v>
       </c>
       <c r="B116" t="n">
-        <v>99147</v>
+        <v>111176</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12511,16 +12567,16 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>219864</v>
+        <v>219677</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -12528,34 +12584,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Fröjel Hallgårds 1:2 3, Gtl</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>693015</v>
+        <v>693103</v>
       </c>
       <c r="R116" t="n">
-        <v>6359102</v>
+        <v>6359146</v>
       </c>
       <c r="S116" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12616,10 +12658,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>116145609</v>
+        <v>117684242</v>
       </c>
       <c r="B117" t="n">
-        <v>99147</v>
+        <v>111176</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12627,16 +12669,16 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>219864</v>
+        <v>219677</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -12644,31 +12686,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Fröjel Hallgårds 1:2 3, Gtl</t>
+          <t>Fröjel, Hallgårds 1:2 (3) N-del, Gtl</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>693006</v>
+        <v>692948</v>
       </c>
       <c r="R117" t="n">
-        <v>6359120</v>
+        <v>6359349</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -12711,11 +12739,6 @@
       </c>
       <c r="AG117" t="b">
         <v>0</v>
-      </c>
-      <c r="AI117" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
@@ -12732,10 +12755,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>116145611</v>
+        <v>112720971</v>
       </c>
       <c r="B118" t="n">
-        <v>99147</v>
+        <v>99141</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12743,51 +12766,38 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>219864</v>
+        <v>219862</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Fröjel Hallgårds 1:2 3, Gtl</t>
+          <t>Styrmansberget, Gtl</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>692988</v>
+        <v>693029</v>
       </c>
       <c r="R118" t="n">
-        <v>6359145</v>
+        <v>6359252</v>
       </c>
       <c r="S118" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -12811,12 +12821,12 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2023-10-14</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2023-10-14</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12827,28 +12837,23 @@
       </c>
       <c r="AG118" t="b">
         <v>0</v>
-      </c>
-      <c r="AI118" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>116145623</v>
+        <v>116145602</v>
       </c>
       <c r="B119" t="n">
         <v>99147</v>
@@ -12878,7 +12883,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -12897,10 +12902,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>693043</v>
+        <v>693052</v>
       </c>
       <c r="R119" t="n">
-        <v>6359214</v>
+        <v>6359090</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -12964,7 +12969,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>116145627</v>
+        <v>116145604</v>
       </c>
       <c r="B120" t="n">
         <v>99147</v>
@@ -12994,7 +12999,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -13013,10 +13018,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>693034</v>
+        <v>693030</v>
       </c>
       <c r="R120" t="n">
-        <v>6359172</v>
+        <v>6359101</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13080,7 +13085,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>116145632</v>
+        <v>116145605</v>
       </c>
       <c r="B121" t="n">
         <v>99147</v>
@@ -13110,7 +13115,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -13129,10 +13134,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>693048</v>
+        <v>693015</v>
       </c>
       <c r="R121" t="n">
-        <v>6359128</v>
+        <v>6359102</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -13196,7 +13201,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>116145633</v>
+        <v>116145609</v>
       </c>
       <c r="B122" t="n">
         <v>99147</v>
@@ -13226,7 +13231,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -13245,13 +13250,13 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>693056</v>
+        <v>693006</v>
       </c>
       <c r="R122" t="n">
-        <v>6359129</v>
+        <v>6359120</v>
       </c>
       <c r="S122" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13312,7 +13317,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>116145638</v>
+        <v>116145611</v>
       </c>
       <c r="B123" t="n">
         <v>99147</v>
@@ -13342,7 +13347,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -13361,13 +13366,13 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>693077</v>
+        <v>692988</v>
       </c>
       <c r="R123" t="n">
-        <v>6359141</v>
+        <v>6359145</v>
       </c>
       <c r="S123" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13428,7 +13433,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>116145639</v>
+        <v>116145623</v>
       </c>
       <c r="B124" t="n">
         <v>99147</v>
@@ -13458,7 +13463,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -13477,10 +13482,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>693103</v>
+        <v>693043</v>
       </c>
       <c r="R124" t="n">
-        <v>6359146</v>
+        <v>6359214</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -13513,11 +13518,6 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2024-04-21</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>två plantor med fläckiga blad.</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13549,7 +13549,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>116145645</v>
+        <v>116145627</v>
       </c>
       <c r="B125" t="n">
         <v>99147</v>
@@ -13579,7 +13579,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -13598,13 +13598,13 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>693193</v>
+        <v>693034</v>
       </c>
       <c r="R125" t="n">
-        <v>6359114</v>
+        <v>6359172</v>
       </c>
       <c r="S125" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -13665,7 +13665,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>116145650</v>
+        <v>116145632</v>
       </c>
       <c r="B126" t="n">
         <v>99147</v>
@@ -13695,7 +13695,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -13714,10 +13714,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>693240</v>
+        <v>693048</v>
       </c>
       <c r="R126" t="n">
-        <v>6359011</v>
+        <v>6359128</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -13781,7 +13781,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>117684243</v>
+        <v>116145633</v>
       </c>
       <c r="B127" t="n">
         <v>99147</v>
@@ -13811,7 +13811,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -13819,19 +13819,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Fröjel, Hallgårds 1:2 (3) N-del, Gtl</t>
+          <t>Fröjel Hallgårds 1:2 3, Gtl</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>692948</v>
+        <v>693056</v>
       </c>
       <c r="R127" t="n">
-        <v>6359349</v>
+        <v>6359129</v>
       </c>
       <c r="S127" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -13871,6 +13876,11 @@
       </c>
       <c r="AG127" t="b">
         <v>0</v>
+      </c>
+      <c r="AI127" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
@@ -13887,48 +13897,62 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>112729437</v>
+        <v>116145638</v>
       </c>
       <c r="B128" t="n">
-        <v>108116</v>
+        <v>99147</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>220079</v>
+        <v>219864</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Fröjel, Gtl</t>
+          <t>Fröjel Hallgårds 1:2 3, Gtl</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>692943</v>
+        <v>693077</v>
       </c>
       <c r="R128" t="n">
-        <v>6359307</v>
+        <v>6359141</v>
       </c>
       <c r="S128" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13952,12 +13976,12 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2023-10-14</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2023-10-14</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13968,81 +13992,80 @@
       </c>
       <c r="AG128" t="b">
         <v>0</v>
+      </c>
+      <c r="AI128" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Alexander Singer, Laritza Pettersson, Helena Björnström, Mikael Jeppson, Erland Lindblad, Thomas Jeppesen</t>
-        </is>
-      </c>
-      <c r="AY128" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna Gotland</t>
-        </is>
-      </c>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>118772968</v>
+        <v>116145639</v>
       </c>
       <c r="B129" t="n">
-        <v>108116</v>
+        <v>99147</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>220079</v>
+        <v>219864</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Fröjel Hallgårds 1:2 3, Gtl</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>693239</v>
+        <v>693103</v>
       </c>
       <c r="R129" t="n">
-        <v>6358916</v>
+        <v>6359146</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -14069,12 +14092,17 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2024-04-21</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>två plantor med fläckiga blad.</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14083,61 +14111,60 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
-      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>Kalkbarrskog</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Gun Ingmansson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>118772971</v>
+        <v>116145645</v>
       </c>
       <c r="B130" t="n">
-        <v>108116</v>
+        <v>99147</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>220079</v>
+        <v>219864</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -14150,21 +14177,19 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Fröjel Hallgårds 1:2 3, Gtl</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>693183</v>
+        <v>693193</v>
       </c>
       <c r="R130" t="n">
-        <v>6358972</v>
+        <v>6359114</v>
       </c>
       <c r="S130" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14188,12 +14213,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14202,59 +14227,67 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
-      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
       <c r="AI130" t="inlineStr">
         <is>
-          <t>Kalkbarrskog</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Gun Ingmansson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>118772974</v>
+        <v>116145650</v>
       </c>
       <c r="B131" t="n">
-        <v>108116</v>
+        <v>99147</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>220079</v>
+        <v>219864</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K131" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -14266,10 +14299,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>693098</v>
+        <v>693240</v>
       </c>
       <c r="R131" t="n">
-        <v>6358999</v>
+        <v>6359011</v>
       </c>
       <c r="S131" t="n">
         <v>5</v>
@@ -14296,12 +14329,12 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14315,55 +14348,55 @@
       </c>
       <c r="AI131" t="inlineStr">
         <is>
-          <t>Kalkbarrskog</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Gun Ingmansson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>118772976</v>
+        <v>117684243</v>
       </c>
       <c r="B132" t="n">
-        <v>108116</v>
+        <v>99147</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>220079</v>
+        <v>219864</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -14371,21 +14404,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Fröjel Hallgårds 1:2 3, Gtl</t>
+          <t>Fröjel, Hallgårds 1:2 (3) N-del, Gtl</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>693032</v>
+        <v>692948</v>
       </c>
       <c r="R132" t="n">
-        <v>6359058</v>
+        <v>6359349</v>
       </c>
       <c r="S132" t="n">
         <v>5</v>
@@ -14412,12 +14440,12 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14428,28 +14456,23 @@
       </c>
       <c r="AG132" t="b">
         <v>0</v>
-      </c>
-      <c r="AI132" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Gun Ingmansson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>118772978</v>
+        <v>112729437</v>
       </c>
       <c r="B133" t="n">
         <v>108116</v>
@@ -14477,26 +14500,17 @@
           <t>(L.) Scop.</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Fröjel Hallgårds 1:2 3, Gtl</t>
+          <t>Fröjel, Gtl</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>693171</v>
+        <v>692943</v>
       </c>
       <c r="R133" t="n">
-        <v>6359066</v>
+        <v>6359307</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14523,17 +14537,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2023-10-14</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>inom 15 m</t>
+          <t>2023-10-14</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14544,31 +14553,30 @@
       </c>
       <c r="AG133" t="b">
         <v>0</v>
-      </c>
-      <c r="AI133" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Gun Ingmansson</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AY133" t="inlineStr"/>
+          <t>Alexander Singer, Laritza Pettersson, Helena Björnström, Mikael Jeppson, Erland Lindblad, Thomas Jeppesen</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>118772965</v>
+        <v>118772968</v>
       </c>
       <c r="B134" t="n">
-        <v>110078</v>
+        <v>108116</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14576,21 +14584,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -14605,22 +14613,24 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Fröjel Hallgårds 1:2 3, Gtl</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>693249</v>
+        <v>693239</v>
       </c>
       <c r="R134" t="n">
-        <v>6358880</v>
+        <v>6358916</v>
       </c>
       <c r="S134" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14658,6 +14668,7 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
+      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
@@ -14681,10 +14692,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>118772969</v>
+        <v>118772971</v>
       </c>
       <c r="B135" t="n">
-        <v>110078</v>
+        <v>108116</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14692,36 +14703,36 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L135" t="inlineStr"/>
@@ -14732,13 +14743,13 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>693235</v>
+        <v>693183</v>
       </c>
       <c r="R135" t="n">
-        <v>6358938</v>
+        <v>6358972</v>
       </c>
       <c r="S135" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -14800,10 +14811,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>118772973</v>
+        <v>118772974</v>
       </c>
       <c r="B136" t="n">
-        <v>110078</v>
+        <v>108116</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14811,27 +14822,27 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="K136" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
@@ -14907,10 +14918,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>118772980</v>
+        <v>118772976</v>
       </c>
       <c r="B137" t="n">
-        <v>110078</v>
+        <v>108116</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14918,27 +14929,36 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
@@ -14947,10 +14967,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>693207</v>
+        <v>693032</v>
       </c>
       <c r="R137" t="n">
-        <v>6359037</v>
+        <v>6359058</v>
       </c>
       <c r="S137" t="n">
         <v>5</v>
@@ -15014,38 +15034,42 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>116145635</v>
+        <v>118772978</v>
       </c>
       <c r="B138" t="n">
-        <v>106156</v>
+        <v>108116</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>221141</v>
+        <v>220079</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
@@ -15054,13 +15078,13 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>693065</v>
+        <v>693171</v>
       </c>
       <c r="R138" t="n">
-        <v>6359134</v>
+        <v>6359066</v>
       </c>
       <c r="S138" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -15084,12 +15108,17 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>inom 15 m</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15103,28 +15132,28 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog</t>
         </is>
       </c>
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>118772977</v>
+        <v>118772965</v>
       </c>
       <c r="B139" t="n">
-        <v>107517</v>
+        <v>110078</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15132,16 +15161,16 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -15161,7 +15190,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
@@ -15170,10 +15199,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>693063</v>
+        <v>693249</v>
       </c>
       <c r="R139" t="n">
-        <v>6359046</v>
+        <v>6358880</v>
       </c>
       <c r="S139" t="n">
         <v>3</v>
@@ -15237,53 +15266,64 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>116145640</v>
+        <v>118772969</v>
       </c>
       <c r="B140" t="n">
-        <v>101326</v>
+        <v>110078</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>222498</v>
+        <v>220299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Fröjel Hallgårds 1:2 3, Gtl</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>693103</v>
+        <v>693235</v>
       </c>
       <c r="R140" t="n">
-        <v>6359146</v>
+        <v>6358938</v>
       </c>
       <c r="S140" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -15307,12 +15347,12 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15321,61 +15361,62 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
+      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog</t>
         </is>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>116145643</v>
+        <v>118772973</v>
       </c>
       <c r="B141" t="n">
-        <v>101326</v>
+        <v>110078</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>222498</v>
+        <v>220299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="K141" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
@@ -15384,10 +15425,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>693156</v>
+        <v>693098</v>
       </c>
       <c r="R141" t="n">
-        <v>6359135</v>
+        <v>6358999</v>
       </c>
       <c r="S141" t="n">
         <v>5</v>
@@ -15414,12 +15455,12 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15433,56 +15474,56 @@
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog</t>
         </is>
       </c>
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>116145648</v>
+        <v>118772980</v>
       </c>
       <c r="B142" t="n">
-        <v>101326</v>
+        <v>110078</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>222498</v>
+        <v>220299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="K142" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
@@ -15491,10 +15532,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>693197</v>
+        <v>693207</v>
       </c>
       <c r="R142" t="n">
-        <v>6359058</v>
+        <v>6359037</v>
       </c>
       <c r="S142" t="n">
         <v>5</v>
@@ -15521,12 +15562,12 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15540,28 +15581,28 @@
       </c>
       <c r="AI142" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog</t>
         </is>
       </c>
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>116145651</v>
+        <v>116145635</v>
       </c>
       <c r="B143" t="n">
-        <v>101326</v>
+        <v>106156</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15569,27 +15610,27 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="K143" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
@@ -15598,10 +15639,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>693240</v>
+        <v>693065</v>
       </c>
       <c r="R143" t="n">
-        <v>6359011</v>
+        <v>6359134</v>
       </c>
       <c r="S143" t="n">
         <v>5</v>
@@ -15665,35 +15706,44 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>116145654</v>
+        <v>118772977</v>
       </c>
       <c r="B144" t="n">
-        <v>101326</v>
+        <v>107517</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>222498</v>
+        <v>221849</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K144" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -15705,13 +15755,13 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>693235</v>
+        <v>693063</v>
       </c>
       <c r="R144" t="n">
-        <v>6358973</v>
+        <v>6359046</v>
       </c>
       <c r="S144" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -15735,12 +15785,12 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15754,25 +15804,25 @@
       </c>
       <c r="AI144" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog</t>
         </is>
       </c>
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>116145656</v>
+        <v>116145640</v>
       </c>
       <c r="B145" t="n">
         <v>101326</v>
@@ -15812,13 +15862,13 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>693253</v>
+        <v>693103</v>
       </c>
       <c r="R145" t="n">
-        <v>6358939</v>
+        <v>6359146</v>
       </c>
       <c r="S145" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -15879,7 +15929,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>116145658</v>
+        <v>116145643</v>
       </c>
       <c r="B146" t="n">
         <v>101326</v>
@@ -15907,16 +15957,7 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I146" t="inlineStr"/>
       <c r="K146" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -15928,10 +15969,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>693275</v>
+        <v>693156</v>
       </c>
       <c r="R146" t="n">
-        <v>6358917</v>
+        <v>6359135</v>
       </c>
       <c r="S146" t="n">
         <v>5</v>
@@ -15995,59 +16036,53 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>120633915</v>
+        <v>116145648</v>
       </c>
       <c r="B147" t="n">
-        <v>87369</v>
+        <v>101326</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>248947</v>
+        <v>222498</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K147" t="inlineStr"/>
-      <c r="N147" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Styrmansberget Flöjel, Gtl</t>
+          <t>Fröjel Hallgårds 1:2 3, Gtl</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>692971</v>
+        <v>693197</v>
       </c>
       <c r="R147" t="n">
-        <v>6359323</v>
+        <v>6359058</v>
       </c>
       <c r="S147" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -16071,12 +16106,12 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16085,82 +16120,76 @@
       <c r="AE147" t="b">
         <v>0</v>
       </c>
-      <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="b">
         <v>0</v>
+      </c>
+      <c r="AI147" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
       </c>
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Uno Skog, Helena Björnström, Carl Jansson, Andreas Öster</t>
-        </is>
-      </c>
-      <c r="AY147" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna Gotland</t>
-        </is>
-      </c>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>120633916</v>
+        <v>116145651</v>
       </c>
       <c r="B148" t="n">
-        <v>87369</v>
+        <v>101326</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>248947</v>
+        <v>222498</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K148" t="inlineStr"/>
-      <c r="N148" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Styrmansberget Flöjel, Gtl</t>
+          <t>Fröjel Hallgårds 1:2 3, Gtl</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>692965</v>
+        <v>693240</v>
       </c>
       <c r="R148" t="n">
-        <v>6359326</v>
+        <v>6359011</v>
       </c>
       <c r="S148" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -16184,12 +16213,12 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16198,71 +16227,76 @@
       <c r="AE148" t="b">
         <v>0</v>
       </c>
-      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
+      </c>
+      <c r="AI148" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
       </c>
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Uno Skog, Helena Björnström, Carl Jansson, Andreas Öster</t>
-        </is>
-      </c>
-      <c r="AY148" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna Gotland</t>
-        </is>
-      </c>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>120631620</v>
+        <v>116145654</v>
       </c>
       <c r="B149" t="n">
-        <v>87262</v>
+        <v>101326</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>248956</v>
+        <v>222498</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Styrmansberget, Fröjel, Gtl</t>
+          <t>Fröjel Hallgårds 1:2 3, Gtl</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>693002</v>
+        <v>693235</v>
       </c>
       <c r="R149" t="n">
-        <v>6359215</v>
+        <v>6358973</v>
       </c>
       <c r="S149" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -16286,12 +16320,12 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16302,68 +16336,74 @@
       </c>
       <c r="AG149" t="b">
         <v>0</v>
+      </c>
+      <c r="AI149" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
       </c>
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Carl Jansson, Helena Björnström, Uno Skog, Andreas Öster</t>
-        </is>
-      </c>
-      <c r="AY149" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna Gotland</t>
-        </is>
-      </c>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>120631626</v>
+        <v>116145656</v>
       </c>
       <c r="B150" t="n">
-        <v>87262</v>
+        <v>101326</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>248956</v>
+        <v>222498</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Styrmansberget, Fröjel, Gtl</t>
+          <t>Fröjel Hallgårds 1:2 3, Gtl</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>692968</v>
+        <v>693253</v>
       </c>
       <c r="R150" t="n">
-        <v>6359295</v>
+        <v>6358939</v>
       </c>
       <c r="S150" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -16387,12 +16427,12 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16403,68 +16443,83 @@
       </c>
       <c r="AG150" t="b">
         <v>0</v>
+      </c>
+      <c r="AI150" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
       </c>
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Carl Jansson, Helena Björnström, Uno Skog, Andreas Öster</t>
-        </is>
-      </c>
-      <c r="AY150" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna Gotland</t>
-        </is>
-      </c>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>120631630</v>
+        <v>116145658</v>
       </c>
       <c r="B151" t="n">
-        <v>87262</v>
+        <v>101326</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>248956</v>
+        <v>222498</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Styrmansberget, Fröjel, Gtl</t>
+          <t>Fröjel Hallgårds 1:2 3, Gtl</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>692965</v>
+        <v>693275</v>
       </c>
       <c r="R151" t="n">
-        <v>6359323</v>
+        <v>6358917</v>
       </c>
       <c r="S151" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -16488,12 +16543,12 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16504,30 +16559,31 @@
       </c>
       <c r="AG151" t="b">
         <v>0</v>
+      </c>
+      <c r="AI151" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
       </c>
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Carl Jansson, Helena Björnström, Uno Skog, Andreas Öster</t>
-        </is>
-      </c>
-      <c r="AY151" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna Gotland</t>
-        </is>
-      </c>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>120633929</v>
+        <v>120633915</v>
       </c>
       <c r="B152" t="n">
-        <v>87262</v>
+        <v>87369</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16535,21 +16591,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>248956</v>
+        <v>248947</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -16562,16 +16618,18 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
           <t>Styrmansberget Flöjel, Gtl</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>692988</v>
+        <v>692971</v>
       </c>
       <c r="R152" t="n">
-        <v>6359257</v>
+        <v>6359323</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16635,10 +16693,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>120633930</v>
+        <v>120633916</v>
       </c>
       <c r="B153" t="n">
-        <v>87262</v>
+        <v>87369</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16646,21 +16704,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>248956</v>
+        <v>248947</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -16673,16 +16731,18 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Styrmansberget Flöjel, Gtl</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>693006</v>
+        <v>692965</v>
       </c>
       <c r="R153" t="n">
-        <v>6359238</v>
+        <v>6359326</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16746,10 +16806,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>112729739</v>
+        <v>120631620</v>
       </c>
       <c r="B154" t="n">
-        <v>90707</v>
+        <v>87262</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16757,34 +16817,34 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>249376</v>
+        <v>248956</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Ullmusseron</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Tricholoma squarrulosum</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Bres.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Fröjel, Gtl</t>
+          <t>Styrmansberget, Fröjel, Gtl</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>692983</v>
+        <v>693002</v>
       </c>
       <c r="R154" t="n">
-        <v>6359358</v>
+        <v>6359215</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16811,12 +16871,12 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2023-10-14</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2023-10-14</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16825,19 +16885,18 @@
       <c r="AE154" t="b">
         <v>0</v>
       </c>
-      <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="b">
         <v>0</v>
       </c>
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Alexander Singer, Helena Björnström, Mikael Jeppson, Laritza Pettersson, Erland Lindblad, Thomas Jeppesen</t>
+          <t>Carl Jansson, Helena Björnström, Uno Skog, Andreas Öster</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
@@ -16848,45 +16907,45 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>112725820</v>
+        <v>120631626</v>
       </c>
       <c r="B155" t="n">
-        <v>87346</v>
+        <v>87262</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Fröjel, Gtl</t>
+          <t>Styrmansberget, Fröjel, Gtl</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>693004</v>
+        <v>692968</v>
       </c>
       <c r="R155" t="n">
-        <v>6359119</v>
+        <v>6359295</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16913,12 +16972,12 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>2023-10-14</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2023-10-14</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16933,12 +16992,12 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Carl Jansson, Helena Björnström, Uno Skog, Andreas Öster</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
@@ -16949,48 +17008,45 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>112725864</v>
+        <v>120631630</v>
       </c>
       <c r="B156" t="n">
-        <v>87346</v>
+        <v>87262</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
-      <c r="J156" t="inlineStr"/>
-      <c r="K156" t="inlineStr"/>
-      <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Fröjel, Gtl</t>
+          <t>Styrmansberget, Fröjel, Gtl</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>693274</v>
+        <v>692965</v>
       </c>
       <c r="R156" t="n">
-        <v>6358982</v>
+        <v>6359323</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17017,12 +17073,12 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2023-10-14</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2023-10-14</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17031,19 +17087,18 @@
       <c r="AE156" t="b">
         <v>0</v>
       </c>
-      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Petra Wikström, Anna Helmersson, Brian Johnson</t>
+          <t>Carl Jansson, Helena Björnström, Uno Skog, Andreas Öster</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
@@ -17054,48 +17109,54 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>112725868</v>
+        <v>120633929</v>
       </c>
       <c r="B157" t="n">
-        <v>87346</v>
+        <v>87262</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr"/>
-      <c r="J157" t="inlineStr"/>
-      <c r="K157" t="inlineStr"/>
-      <c r="N157" t="inlineStr"/>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Fröjel, Gtl</t>
+          <t>Styrmansberget Flöjel, Gtl</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>692980</v>
+        <v>692988</v>
       </c>
       <c r="R157" t="n">
-        <v>6359112</v>
+        <v>6359257</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17122,12 +17183,12 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2023-10-14</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2023-10-14</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17143,12 +17204,12 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Petra Wikström, Anna Helmersson, Brian Johnson</t>
+          <t>Uno Skog, Helena Björnström, Carl Jansson, Andreas Öster</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
@@ -17159,48 +17220,54 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>112742187</v>
+        <v>120633930</v>
       </c>
       <c r="B158" t="n">
-        <v>87346</v>
+        <v>87262</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr"/>
-      <c r="J158" t="inlineStr"/>
-      <c r="K158" t="inlineStr"/>
-      <c r="N158" t="inlineStr"/>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Fröjel, Gtl</t>
+          <t>Styrmansberget Flöjel, Gtl</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>693270</v>
+        <v>693006</v>
       </c>
       <c r="R158" t="n">
-        <v>6358918</v>
+        <v>6359238</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17227,12 +17294,12 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2023-10-14</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2023-10-14</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17248,12 +17315,12 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Rut Folke</t>
+          <t>Uno Skog, Helena Björnström, Carl Jansson, Andreas Öster</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr">
@@ -17264,32 +17331,32 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>112772709</v>
+        <v>112729739</v>
       </c>
       <c r="B159" t="n">
-        <v>87346</v>
+        <v>90707</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6003295</v>
+        <v>249376</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Ullmusseron</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Tricholoma squarrulosum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Bres.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17299,10 +17366,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>693122</v>
+        <v>692983</v>
       </c>
       <c r="R159" t="n">
-        <v>6359010</v>
+        <v>6359358</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17343,18 +17410,19 @@
       <c r="AE159" t="b">
         <v>0</v>
       </c>
+      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alexander Singer, Helena Björnström, Mikael Jeppson, Laritza Pettersson, Erland Lindblad, Thomas Jeppesen</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
@@ -17365,7 +17433,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>112772710</v>
+        <v>112725820</v>
       </c>
       <c r="B160" t="n">
         <v>87346</v>
@@ -17400,10 +17468,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>693014</v>
+        <v>693004</v>
       </c>
       <c r="R160" t="n">
-        <v>6359071</v>
+        <v>6359119</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17450,12 +17518,12 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
@@ -17466,7 +17534,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>112772711</v>
+        <v>112725864</v>
       </c>
       <c r="B161" t="n">
         <v>87346</v>
@@ -17495,16 +17563,19 @@
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Fröjel, Gtl</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>692977</v>
+        <v>693274</v>
       </c>
       <c r="R161" t="n">
-        <v>6359116</v>
+        <v>6358982</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17545,18 +17616,19 @@
       <c r="AE161" t="b">
         <v>0</v>
       </c>
+      <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="b">
         <v>0</v>
       </c>
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Petra Wikström, Anna Helmersson, Brian Johnson</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
@@ -17567,7 +17639,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>112791688</v>
+        <v>112725868</v>
       </c>
       <c r="B162" t="n">
         <v>87346</v>
@@ -17596,16 +17668,19 @@
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Fröjel-Sigdarve, Gtl</t>
+          <t>Fröjel, Gtl</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>692950</v>
+        <v>692980</v>
       </c>
       <c r="R162" t="n">
-        <v>6359365</v>
+        <v>6359112</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17646,18 +17721,19 @@
       <c r="AE162" t="b">
         <v>0</v>
       </c>
+      <c r="AF162" t="inlineStr"/>
       <c r="AG162" t="b">
         <v>0</v>
       </c>
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Petra Wikström, Anna Helmersson, Brian Johnson</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
@@ -17668,7 +17744,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>112791690</v>
+        <v>112742187</v>
       </c>
       <c r="B163" t="n">
         <v>87346</v>
@@ -17697,16 +17773,19 @@
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Fröjel-Sigdarve, Gtl</t>
+          <t>Fröjel, Gtl</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>693013</v>
+        <v>693270</v>
       </c>
       <c r="R163" t="n">
-        <v>6359247</v>
+        <v>6358918</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17747,18 +17826,19 @@
       <c r="AE163" t="b">
         <v>0</v>
       </c>
+      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Rut Folke</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
@@ -17769,7 +17849,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>112791692</v>
+        <v>112772709</v>
       </c>
       <c r="B164" t="n">
         <v>87346</v>
@@ -17800,14 +17880,14 @@
       <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Fröjel-Sigdarve, Gtl</t>
+          <t>Fröjel, Gtl</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>692892</v>
+        <v>693122</v>
       </c>
       <c r="R164" t="n">
-        <v>6359313</v>
+        <v>6359010</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17854,12 +17934,12 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
@@ -17870,7 +17950,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>120631622</v>
+        <v>112772710</v>
       </c>
       <c r="B165" t="n">
         <v>87346</v>
@@ -17901,14 +17981,14 @@
       <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Styrmansberget, Fröjel, Gtl</t>
+          <t>Fröjel, Gtl</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>693000</v>
+        <v>693014</v>
       </c>
       <c r="R165" t="n">
-        <v>6359215</v>
+        <v>6359071</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17935,12 +18015,12 @@
       </c>
       <c r="Y165" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2023-10-14</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2023-10-14</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17955,12 +18035,12 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Carl Jansson, Helena Björnström, Uno Skog, Andreas Öster</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
@@ -17971,7 +18051,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>120633919</v>
+        <v>112772711</v>
       </c>
       <c r="B166" t="n">
         <v>87346</v>
@@ -17999,26 +18079,17 @@
           <t>M.M.Moser</t>
         </is>
       </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J166" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Styrmansberget Flöjel, Gtl</t>
+          <t>Fröjel, Gtl</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>692950</v>
+        <v>692977</v>
       </c>
       <c r="R166" t="n">
-        <v>6359351</v>
+        <v>6359116</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18045,12 +18116,12 @@
       </c>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2023-10-14</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2023-10-14</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18065,12 +18136,12 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Uno Skog, Helena Björnström, Carl Jansson, Andreas Öster</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr">
@@ -18081,10 +18152,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>96929844</v>
+        <v>112791688</v>
       </c>
       <c r="B167" t="n">
-        <v>87312</v>
+        <v>87346</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18092,34 +18163,34 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6037417</v>
+        <v>6003295</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Denisespindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Cortinarius olivaceodionysae</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>A.Ortega &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Fröjel Ö, Gtl</t>
+          <t>Fröjel-Sigdarve, Gtl</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>693021</v>
+        <v>692950</v>
       </c>
       <c r="R167" t="n">
-        <v>6359325</v>
+        <v>6359365</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18146,12 +18217,12 @@
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2023-10-14</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2023-10-14</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18174,14 +18245,18 @@
           <t>Helena Björnström</t>
         </is>
       </c>
-      <c r="AY167" t="inlineStr"/>
+      <c r="AY167" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>96929845</v>
+        <v>112791690</v>
       </c>
       <c r="B168" t="n">
-        <v>87312</v>
+        <v>87346</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18189,34 +18264,34 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6037417</v>
+        <v>6003295</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Denisespindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Cortinarius olivaceodionysae</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>A.Ortega &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Fröjel Ö, Gtl</t>
+          <t>Fröjel-Sigdarve, Gtl</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>693032</v>
+        <v>693013</v>
       </c>
       <c r="R168" t="n">
-        <v>6359266</v>
+        <v>6359247</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18243,12 +18318,12 @@
       </c>
       <c r="Y168" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2023-10-14</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2023-10-14</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -18271,14 +18346,18 @@
           <t>Helena Björnström</t>
         </is>
       </c>
-      <c r="AY168" t="inlineStr"/>
+      <c r="AY168" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>112791678</v>
+        <v>112791692</v>
       </c>
       <c r="B169" t="n">
-        <v>93211</v>
+        <v>87346</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18286,19 +18365,23 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6047725</v>
+        <v>6003295</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H169" t="inlineStr"/>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
@@ -18306,10 +18389,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>692995</v>
+        <v>692892</v>
       </c>
       <c r="R169" t="n">
-        <v>6359345</v>
+        <v>6359313</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18372,45 +18455,45 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>112725813</v>
+        <v>120631622</v>
       </c>
       <c r="B170" t="n">
-        <v>87193</v>
+        <v>87346</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Fröjel, Gtl</t>
+          <t>Styrmansberget, Fröjel, Gtl</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>693328</v>
+        <v>693000</v>
       </c>
       <c r="R170" t="n">
-        <v>6358906</v>
+        <v>6359215</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18437,12 +18520,12 @@
       </c>
       <c r="Y170" t="inlineStr">
         <is>
-          <t>2023-10-14</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>2023-10-14</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18457,12 +18540,12 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Carl Jansson, Helena Björnström, Uno Skog, Andreas Öster</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr">
@@ -18473,45 +18556,54 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>113015018</v>
+        <v>120633919</v>
       </c>
       <c r="B171" t="n">
-        <v>91680</v>
+        <v>87346</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>3215</v>
+        <v>6003295</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr"/>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Fröjel, Gtl</t>
+          <t>Styrmansberget Flöjel, Gtl</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>693291</v>
+        <v>692950</v>
       </c>
       <c r="R171" t="n">
-        <v>6358849</v>
+        <v>6359351</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18538,12 +18630,12 @@
       </c>
       <c r="Y171" t="inlineStr">
         <is>
-          <t>2023-10-14</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>2023-10-14</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18558,12 +18650,12 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Michael Krikorev</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Michael Krikorev</t>
+          <t>Uno Skog, Helena Björnström, Carl Jansson, Andreas Öster</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr">
@@ -18574,45 +18666,45 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>112725835</v>
+        <v>96929844</v>
       </c>
       <c r="B172" t="n">
-        <v>87309</v>
+        <v>87312</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>3674</v>
+        <v>6037417</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Denisespindling</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius olivaceodionysae</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>A.Ortega &amp; al.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Fröjel, Gtl</t>
+          <t>Fröjel Ö, Gtl</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>693316</v>
+        <v>693021</v>
       </c>
       <c r="R172" t="n">
-        <v>6358892</v>
+        <v>6359325</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18639,12 +18731,12 @@
       </c>
       <c r="Y172" t="inlineStr">
         <is>
-          <t>2023-10-14</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>2023-10-14</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18659,64 +18751,60 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
-        </is>
-      </c>
-      <c r="AY172" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna Gotland</t>
-        </is>
-      </c>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>116145662</v>
+        <v>96929845</v>
       </c>
       <c r="B173" t="n">
-        <v>111176</v>
+        <v>87312</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>219677</v>
+        <v>6037417</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Denisespindling</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Cortinarius olivaceodionysae</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>A.Ortega &amp; al.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Fröjel Hallgårds 1:2 3, Gtl</t>
+          <t>Fröjel Ö, Gtl</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>693323</v>
+        <v>693032</v>
       </c>
       <c r="R173" t="n">
-        <v>6358910</v>
+        <v>6359266</v>
       </c>
       <c r="S173" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -18740,12 +18828,12 @@
       </c>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -18756,74 +18844,60 @@
       </c>
       <c r="AG173" t="b">
         <v>0</v>
-      </c>
-      <c r="AI173" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>116145660</v>
+        <v>112791678</v>
       </c>
       <c r="B174" t="n">
-        <v>101326</v>
+        <v>93211</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>222498</v>
+        <v>6047725</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr"/>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Fröjel Hallgårds 1:2 3, Gtl</t>
+          <t>Fröjel-Sigdarve, Gtl</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>693303</v>
+        <v>692995</v>
       </c>
       <c r="R174" t="n">
-        <v>6358903</v>
+        <v>6359345</v>
       </c>
       <c r="S174" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -18847,12 +18921,12 @@
       </c>
       <c r="Y174" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2023-10-14</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2023-10-14</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -18863,74 +18937,68 @@
       </c>
       <c r="AG174" t="b">
         <v>0</v>
-      </c>
-      <c r="AI174" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AY174" t="inlineStr"/>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY174" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>116145663</v>
+        <v>112725813</v>
       </c>
       <c r="B175" t="n">
-        <v>101326</v>
+        <v>87193</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>222498</v>
+        <v>424</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
-      <c r="K175" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Fröjel Hallgårds 1:2 3, Gtl</t>
+          <t>Fröjel, Gtl</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>693323</v>
+        <v>693328</v>
       </c>
       <c r="R175" t="n">
-        <v>6358910</v>
+        <v>6358906</v>
       </c>
       <c r="S175" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -18954,12 +19022,12 @@
       </c>
       <c r="Y175" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2023-10-14</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2023-10-14</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -18970,69 +19038,65 @@
       </c>
       <c r="AG175" t="b">
         <v>0</v>
-      </c>
-      <c r="AI175" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AY175" t="inlineStr"/>
+          <t>Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AY175" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>112725869</v>
+        <v>113015018</v>
       </c>
       <c r="B176" t="n">
-        <v>87346</v>
+        <v>91680</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6003295</v>
+        <v>3215</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
-      <c r="J176" t="inlineStr"/>
-      <c r="K176" t="inlineStr"/>
-      <c r="N176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
           <t>Fröjel, Gtl</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>693292</v>
+        <v>693291</v>
       </c>
       <c r="R176" t="n">
-        <v>6358937</v>
+        <v>6358849</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19073,19 +19137,18 @@
       <c r="AE176" t="b">
         <v>0</v>
       </c>
-      <c r="AF176" t="inlineStr"/>
       <c r="AG176" t="b">
         <v>0</v>
       </c>
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Michael Krikorev</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Petra Wikström, Anna Helmersson, Brian Johnson</t>
+          <t>Michael Krikorev</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr">
@@ -19096,48 +19159,45 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>112742186</v>
+        <v>112725835</v>
       </c>
       <c r="B177" t="n">
-        <v>87346</v>
+        <v>87309</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
-      <c r="J177" t="inlineStr"/>
-      <c r="K177" t="inlineStr"/>
-      <c r="N177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
           <t>Fröjel, Gtl</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>693292</v>
+        <v>693316</v>
       </c>
       <c r="R177" t="n">
-        <v>6358925</v>
+        <v>6358892</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19178,19 +19238,18 @@
       <c r="AE177" t="b">
         <v>0</v>
       </c>
-      <c r="AF177" t="inlineStr"/>
       <c r="AG177" t="b">
         <v>0</v>
       </c>
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Rut Folke</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr">
@@ -19201,51 +19260,48 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>112742188</v>
+        <v>116145662</v>
       </c>
       <c r="B178" t="n">
-        <v>87346</v>
+        <v>111176</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6003295</v>
+        <v>219677</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
-      <c r="J178" t="inlineStr"/>
-      <c r="K178" t="inlineStr"/>
-      <c r="N178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Fröjel, Gtl</t>
+          <t>Fröjel Hallgårds 1:2 3, Gtl</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>693312</v>
+        <v>693323</v>
       </c>
       <c r="R178" t="n">
-        <v>6358896</v>
+        <v>6358910</v>
       </c>
       <c r="S178" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -19269,12 +19325,12 @@
       </c>
       <c r="Y178" t="inlineStr">
         <is>
-          <t>2023-10-14</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>2023-10-14</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -19285,68 +19341,74 @@
       </c>
       <c r="AG178" t="b">
         <v>0</v>
+      </c>
+      <c r="AI178" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
       </c>
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Rut Folke</t>
-        </is>
-      </c>
-      <c r="AY178" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna Gotland</t>
-        </is>
-      </c>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>112772712</v>
+        <v>116145660</v>
       </c>
       <c r="B179" t="n">
-        <v>87346</v>
+        <v>101326</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6003295</v>
+        <v>222498</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Fröjel, Gtl</t>
+          <t>Fröjel Hallgårds 1:2 3, Gtl</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>693291</v>
+        <v>693303</v>
       </c>
       <c r="R179" t="n">
-        <v>6358897</v>
+        <v>6358903</v>
       </c>
       <c r="S179" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -19370,12 +19432,12 @@
       </c>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>2023-10-14</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>2023-10-14</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19386,68 +19448,74 @@
       </c>
       <c r="AG179" t="b">
         <v>0</v>
+      </c>
+      <c r="AI179" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
       </c>
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY179" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna Gotland</t>
-        </is>
-      </c>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>113015020</v>
+        <v>116145663</v>
       </c>
       <c r="B180" t="n">
-        <v>87346</v>
+        <v>101326</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6003295</v>
+        <v>222498</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Fröjel, Gtl</t>
+          <t>Fröjel Hallgårds 1:2 3, Gtl</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>693288</v>
+        <v>693323</v>
       </c>
       <c r="R180" t="n">
-        <v>6358847</v>
+        <v>6358910</v>
       </c>
       <c r="S180" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -19471,12 +19539,12 @@
       </c>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>2023-10-14</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>2023-10-14</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -19487,27 +19555,28 @@
       </c>
       <c r="AG180" t="b">
         <v>0</v>
+      </c>
+      <c r="AI180" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
       </c>
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Michael Krikorev</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Michael Krikorev</t>
-        </is>
-      </c>
-      <c r="AY180" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna Gotland</t>
-        </is>
-      </c>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>113015021</v>
+        <v>112725869</v>
       </c>
       <c r="B181" t="n">
         <v>87346</v>
@@ -19536,16 +19605,19 @@
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
+      <c r="K181" t="inlineStr"/>
+      <c r="N181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
           <t>Fröjel, Gtl</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>693331</v>
+        <v>693292</v>
       </c>
       <c r="R181" t="n">
-        <v>6358889</v>
+        <v>6358937</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19586,21 +19658,534 @@
       <c r="AE181" t="b">
         <v>0</v>
       </c>
+      <c r="AF181" t="inlineStr"/>
       <c r="AG181" t="b">
         <v>0</v>
       </c>
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AX181" t="inlineStr">
+        <is>
+          <t>Petra Wikström, Anna Helmersson, Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AY181" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>112742186</v>
+      </c>
+      <c r="B182" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
+      <c r="N182" t="inlineStr"/>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>Fröjel, Gtl</t>
+        </is>
+      </c>
+      <c r="Q182" t="n">
+        <v>693292</v>
+      </c>
+      <c r="R182" t="n">
+        <v>6358925</v>
+      </c>
+      <c r="S182" t="n">
+        <v>10</v>
+      </c>
+      <c r="T182" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V182" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W182" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y182" t="inlineStr">
+        <is>
+          <t>2023-10-14</t>
+        </is>
+      </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>2023-10-14</t>
+        </is>
+      </c>
+      <c r="AD182" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE182" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF182" t="inlineStr"/>
+      <c r="AG182" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT182" t="inlineStr"/>
+      <c r="AW182" t="inlineStr">
+        <is>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AX182" t="inlineStr">
+        <is>
+          <t>Rut Folke</t>
+        </is>
+      </c>
+      <c r="AY182" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>112742188</v>
+      </c>
+      <c r="B183" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr"/>
+      <c r="J183" t="inlineStr"/>
+      <c r="K183" t="inlineStr"/>
+      <c r="N183" t="inlineStr"/>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>Fröjel, Gtl</t>
+        </is>
+      </c>
+      <c r="Q183" t="n">
+        <v>693312</v>
+      </c>
+      <c r="R183" t="n">
+        <v>6358896</v>
+      </c>
+      <c r="S183" t="n">
+        <v>10</v>
+      </c>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V183" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W183" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y183" t="inlineStr">
+        <is>
+          <t>2023-10-14</t>
+        </is>
+      </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>2023-10-14</t>
+        </is>
+      </c>
+      <c r="AD183" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE183" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG183" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT183" t="inlineStr"/>
+      <c r="AW183" t="inlineStr">
+        <is>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AX183" t="inlineStr">
+        <is>
+          <t>Rut Folke</t>
+        </is>
+      </c>
+      <c r="AY183" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>112772712</v>
+      </c>
+      <c r="B184" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr"/>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>Fröjel, Gtl</t>
+        </is>
+      </c>
+      <c r="Q184" t="n">
+        <v>693291</v>
+      </c>
+      <c r="R184" t="n">
+        <v>6358897</v>
+      </c>
+      <c r="S184" t="n">
+        <v>10</v>
+      </c>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W184" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y184" t="inlineStr">
+        <is>
+          <t>2023-10-14</t>
+        </is>
+      </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>2023-10-14</t>
+        </is>
+      </c>
+      <c r="AD184" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE184" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG184" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT184" t="inlineStr"/>
+      <c r="AW184" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX184" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY184" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>113015020</v>
+      </c>
+      <c r="B185" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>Fröjel, Gtl</t>
+        </is>
+      </c>
+      <c r="Q185" t="n">
+        <v>693288</v>
+      </c>
+      <c r="R185" t="n">
+        <v>6358847</v>
+      </c>
+      <c r="S185" t="n">
+        <v>10</v>
+      </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V185" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W185" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y185" t="inlineStr">
+        <is>
+          <t>2023-10-14</t>
+        </is>
+      </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>2023-10-14</t>
+        </is>
+      </c>
+      <c r="AD185" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE185" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG185" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT185" t="inlineStr"/>
+      <c r="AW185" t="inlineStr">
+        <is>
           <t>Michael Krikorev</t>
         </is>
       </c>
-      <c r="AX181" t="inlineStr">
+      <c r="AX185" t="inlineStr">
         <is>
           <t>Michael Krikorev</t>
         </is>
       </c>
-      <c r="AY181" t="inlineStr">
+      <c r="AY185" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>113015021</v>
+      </c>
+      <c r="B186" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr"/>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>Fröjel, Gtl</t>
+        </is>
+      </c>
+      <c r="Q186" t="n">
+        <v>693331</v>
+      </c>
+      <c r="R186" t="n">
+        <v>6358889</v>
+      </c>
+      <c r="S186" t="n">
+        <v>10</v>
+      </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W186" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y186" t="inlineStr">
+        <is>
+          <t>2023-10-14</t>
+        </is>
+      </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>2023-10-14</t>
+        </is>
+      </c>
+      <c r="AD186" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE186" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG186" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT186" t="inlineStr"/>
+      <c r="AW186" t="inlineStr">
+        <is>
+          <t>Michael Krikorev</t>
+        </is>
+      </c>
+      <c r="AX186" t="inlineStr">
+        <is>
+          <t>Michael Krikorev</t>
+        </is>
+      </c>
+      <c r="AY186" t="inlineStr">
         <is>
           <t>Kalkbarrianerna Gotland</t>
         </is>

--- a/artfynd/A 14450-2023 artfynd.xlsx
+++ b/artfynd/A 14450-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY186"/>
+  <dimension ref="A1:AZ186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96929836</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112725813</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -971,6 +986,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112729449</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1094,6 +1114,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120619632</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1195,6 +1220,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120631625</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1296,6 +1326,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120631628</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1402,6 +1437,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120633917</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1506,6 +1546,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120634096</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1603,6 +1648,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112791716</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1700,6 +1750,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120631629</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1806,6 +1861,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120633934</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1908,6 +1968,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112725831</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2009,6 +2074,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112772717</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2134,6 +2204,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112586313</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2235,6 +2310,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112587028</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2336,6 +2416,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112725821</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2437,6 +2522,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112791707</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2535,6 +2625,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112721794</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2636,6 +2731,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120631623</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2756,6 +2856,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112586306</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2876,6 +2981,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112586310</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2996,6 +3106,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112586312</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3094,6 +3209,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112720128</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3193,6 +3313,11 @@
       <c r="AY25" t="inlineStr">
         <is>
           <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112725810</t>
         </is>
       </c>
     </row>
@@ -3300,6 +3425,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112725856</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3405,6 +3535,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112725857</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3510,6 +3645,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112725858</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3615,6 +3755,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112725859</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3716,6 +3861,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112729438</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3817,6 +3967,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112729734</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3918,6 +4073,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112791664</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4019,6 +4179,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112791666</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4120,6 +4285,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112791668</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4219,6 +4389,11 @@
       <c r="AY35" t="inlineStr">
         <is>
           <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120631632</t>
         </is>
       </c>
     </row>
@@ -4325,6 +4500,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120634087</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4422,6 +4602,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96929833</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4523,6 +4708,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112587018</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4624,6 +4814,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112725814</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4725,6 +4920,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112772707</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4826,6 +5026,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113015018</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4927,6 +5132,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112729450</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5028,6 +5238,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112725834</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5127,6 +5342,11 @@
       <c r="AY44" t="inlineStr">
         <is>
           <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112725835</t>
         </is>
       </c>
     </row>
@@ -5234,6 +5454,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112725881</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5339,6 +5564,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112725882</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5444,6 +5674,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112742195</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5549,6 +5784,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112742198</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5654,6 +5894,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112742199</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5755,6 +6000,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112772723</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5856,6 +6106,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112791724</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5957,6 +6212,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113015030</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6058,6 +6318,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113015031</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6159,6 +6424,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113015032</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6260,6 +6530,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113015033</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6361,6 +6636,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120631631</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6462,6 +6742,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112725832</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6563,6 +6848,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112729448</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6664,6 +6954,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112729753</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6765,6 +7060,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112791717</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6866,6 +7166,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112791718</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6967,6 +7272,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113015016</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7068,6 +7378,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113015017</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7178,6 +7493,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120633938</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7279,6 +7599,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120633940</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7380,6 +7705,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112725816</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7481,6 +7811,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112725817</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7582,6 +7917,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112772708</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7681,6 +8021,11 @@
       <c r="AY69" t="inlineStr">
         <is>
           <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112791686</t>
         </is>
       </c>
     </row>
@@ -7788,6 +8133,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112585363</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7893,6 +8243,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112585364</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7998,6 +8353,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112585365</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8118,6 +8478,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112586308</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8238,6 +8603,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112586309</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8358,6 +8728,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112586311</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8459,6 +8834,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112587033</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8560,6 +8940,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112587034</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8658,6 +9043,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112721191</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8760,6 +9150,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112725822</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8861,6 +9256,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112725824</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8962,6 +9362,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112725825</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9063,6 +9468,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112725826</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9162,6 +9572,11 @@
       <c r="AY83" t="inlineStr">
         <is>
           <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112725827</t>
         </is>
       </c>
     </row>
@@ -9269,6 +9684,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112725872</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9374,6 +9794,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112725873</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9475,6 +9900,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112729447</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9576,6 +10006,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112729452</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9677,6 +10112,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112729454</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9776,6 +10216,11 @@
       <c r="AY89" t="inlineStr">
         <is>
           <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112729749</t>
         </is>
       </c>
     </row>
@@ -9882,6 +10327,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112742189</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9983,6 +10433,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112772715</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10084,6 +10539,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112791709</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10185,6 +10645,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112791710</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10286,6 +10751,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112791711</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10387,6 +10857,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112791712</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10488,6 +10963,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113015022</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10585,6 +11065,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96929842</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10686,6 +11171,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112729451</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10787,6 +11277,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112791706</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10897,6 +11392,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120633922</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10995,6 +11495,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16871240</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11100,6 +11605,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112791714</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11205,6 +11715,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112791715</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11306,6 +11821,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120633924</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11432,6 +11952,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118773230</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11558,6 +12083,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118773232</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11677,6 +12207,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134685906</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11796,6 +12331,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134685911</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11915,6 +12455,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134685915</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12034,6 +12579,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134685916</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12143,6 +12693,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134685914</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12244,6 +12799,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112791663</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12341,6 +12901,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96929839</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12443,6 +13008,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116145613</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12545,6 +13115,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116145614</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12652,6 +13227,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116145615</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12754,6 +13334,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116145620</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12856,6 +13441,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116145630</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12958,6 +13548,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116145641</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13060,6 +13655,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116145662</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13157,6 +13757,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117684242</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13255,6 +13860,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112720971</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13371,6 +13981,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116145602</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13487,6 +14102,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116145604</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13603,6 +14223,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116145605</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13719,6 +14344,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116145609</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13835,6 +14465,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116145611</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13951,6 +14586,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116145623</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14067,6 +14707,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116145627</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14183,6 +14828,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116145632</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14299,6 +14949,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116145633</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14415,6 +15070,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116145638</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14536,6 +15196,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116145639</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14652,6 +15317,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116145645</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14768,6 +15438,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116145650</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14874,6 +15549,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117684243</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14975,6 +15655,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112729437</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -15094,6 +15779,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118772968</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -15213,6 +15903,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118772971</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -15320,6 +16015,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118772974</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -15436,6 +16136,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118772976</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -15552,6 +16257,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118772978</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -15668,6 +16378,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118772965</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15787,6 +16502,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118772969</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -15894,6 +16614,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118772973</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -16001,6 +16726,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118772980</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -16108,6 +16838,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116145635</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -16224,6 +16959,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118772977</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -16331,6 +17071,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116145640</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -16438,6 +17183,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116145643</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -16545,6 +17295,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116145648</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -16652,6 +17407,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116145651</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -16759,6 +17519,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116145654</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -16866,6 +17631,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116145656</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -16982,6 +17752,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116145658</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -17089,6 +17864,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116145660</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -17196,6 +17976,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116145663</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -17309,6 +18094,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120633915</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -17422,6 +18212,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120633916</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -17523,6 +18318,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120631620</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -17624,6 +18424,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120631626</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -17725,6 +18530,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120631630</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -17836,6 +18646,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120633929</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -17947,6 +18762,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120633930</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -18049,6 +18869,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112729739</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -18148,6 +18973,11 @@
       <c r="AY166" t="inlineStr">
         <is>
           <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112725820</t>
         </is>
       </c>
     </row>
@@ -18255,6 +19085,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112725864</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -18360,6 +19195,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112725868</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -18465,6 +19305,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112725869</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -18570,6 +19415,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112742186</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -18675,6 +19525,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112742187</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -18779,6 +19634,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112742188</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -18880,6 +19740,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112772709</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -18981,6 +19846,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112772710</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -19082,6 +19952,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112772711</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -19183,6 +20058,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112772712</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -19284,6 +20164,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112791688</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -19385,6 +20270,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112791690</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -19486,6 +20376,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112791692</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -19587,6 +20482,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113015020</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -19688,6 +20588,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113015021</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -19789,6 +20694,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120631622</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -19899,6 +20809,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120633919</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -19996,6 +20911,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96929844</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -20093,6 +21013,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96929845</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -20190,8 +21115,200 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112791678</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>